--- a/Luaban/MiniTemplate/Datas/#SkillInfo.xlsx
+++ b/Luaban/MiniTemplate/Datas/#SkillInfo.xlsx
@@ -1697,13 +1697,15 @@
         <v>55</v>
       </c>
       <c r="G9" s="4">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>56</v>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>沿当前朝向滑行，可连续使用。</t>
+        </is>
       </c>
       <c r="J9" s="4">
         <v>41</v>
@@ -1718,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O9" s="4">
         <v>0</v>
